--- a/censo.xlsx
+++ b/censo.xlsx
@@ -83,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -91,6 +91,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -437,6 +438,7 @@
       <c r="C2" s="1">
         <v>1.2</v>
       </c>
+      <c r="D2" s="3"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -448,6 +450,7 @@
       <c r="C3" s="1">
         <v>1.4</v>
       </c>
+      <c r="D3" s="3"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -459,6 +462,7 @@
       <c r="C4" s="1">
         <v>1.45</v>
       </c>
+      <c r="D4" s="3"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -470,6 +474,7 @@
       <c r="C5" s="1">
         <v>1.8</v>
       </c>
+      <c r="D5" s="3"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -481,6 +486,7 @@
       <c r="C6" s="1">
         <v>2</v>
       </c>
+      <c r="D6" s="3"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -492,6 +498,7 @@
       <c r="C7" s="1">
         <v>2.2000000000000002</v>
       </c>
+      <c r="D7" s="3"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
@@ -503,6 +510,7 @@
       <c r="C8" s="1">
         <v>2.4</v>
       </c>
+      <c r="D8" s="3"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
@@ -514,6 +522,7 @@
       <c r="C9" s="1">
         <v>2.6</v>
       </c>
+      <c r="D9" s="3"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
@@ -525,6 +534,7 @@
       <c r="C10" s="1">
         <v>2.8</v>
       </c>
+      <c r="D10" s="3"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
@@ -536,6 +546,7 @@
       <c r="C11" s="1">
         <v>3</v>
       </c>
+      <c r="D11" s="3"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
@@ -547,6 +558,7 @@
       <c r="C12" s="1">
         <v>3.2</v>
       </c>
+      <c r="D12" s="3"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
@@ -558,6 +570,7 @@
       <c r="C13" s="1">
         <v>3.4</v>
       </c>
+      <c r="D13" s="3"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
@@ -569,6 +582,7 @@
       <c r="C14" s="1">
         <v>3.6</v>
       </c>
+      <c r="D14" s="3"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
@@ -580,6 +594,7 @@
       <c r="C15" s="1">
         <v>3.8</v>
       </c>
+      <c r="D15" s="3"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
@@ -591,6 +606,7 @@
       <c r="C16" s="1">
         <v>4</v>
       </c>
+      <c r="D16" s="3"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
@@ -602,6 +618,7 @@
       <c r="C17" s="1">
         <v>4.2</v>
       </c>
+      <c r="D17" s="3"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
@@ -613,6 +630,7 @@
       <c r="C18" s="1">
         <v>4.4000000000000004</v>
       </c>
+      <c r="D18" s="3"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
@@ -624,6 +642,7 @@
       <c r="C19" s="1">
         <v>4.5999999999999996</v>
       </c>
+      <c r="D19" s="3"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
@@ -635,6 +654,7 @@
       <c r="C20" s="1">
         <v>4.8</v>
       </c>
+      <c r="D20" s="3"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
@@ -646,6 +666,7 @@
       <c r="C21" s="1">
         <v>5</v>
       </c>
+      <c r="D21" s="3"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
@@ -657,6 +678,7 @@
       <c r="C22" s="1">
         <v>5.2</v>
       </c>
+      <c r="D22" s="3"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
@@ -668,6 +690,7 @@
       <c r="C23" s="1">
         <v>5.4</v>
       </c>
+      <c r="D23" s="3"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
@@ -679,6 +702,7 @@
       <c r="C24" s="1">
         <v>5.6</v>
       </c>
+      <c r="D24" s="3"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
@@ -690,6 +714,9 @@
       <c r="C25" s="1">
         <v>5.8</v>
       </c>
+      <c r="D25" s="3">
+        <v>1121894592</v>
+      </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
@@ -701,6 +728,7 @@
       <c r="C26" s="1">
         <v>6</v>
       </c>
+      <c r="D26" s="3"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
@@ -712,6 +740,7 @@
       <c r="C27" s="1">
         <v>6.2</v>
       </c>
+      <c r="D27" s="3"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
@@ -723,6 +752,7 @@
       <c r="C28" s="1">
         <v>6.4</v>
       </c>
+      <c r="D28" s="3"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
@@ -734,6 +764,7 @@
       <c r="C29" s="1">
         <v>6.6</v>
       </c>
+      <c r="D29" s="3"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
@@ -745,6 +776,7 @@
       <c r="C30" s="1">
         <v>6.8</v>
       </c>
+      <c r="D30" s="3"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
@@ -756,7 +788,7 @@
       <c r="C31" s="1">
         <v>7</v>
       </c>
-      <c r="D31">
+      <c r="D31" s="3">
         <v>1121894592</v>
       </c>
     </row>
@@ -770,8 +802,9 @@
       <c r="C32" s="1">
         <v>7.2</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D32" s="3"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>3</v>
       </c>
@@ -781,8 +814,9 @@
       <c r="C33" s="1">
         <v>7.4</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D33" s="3"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>3</v>
       </c>
@@ -792,8 +826,9 @@
       <c r="C34" s="1">
         <v>7.6</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D34" s="3"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>3</v>
       </c>
@@ -803,8 +838,9 @@
       <c r="C35" s="1">
         <v>7.8</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D35" s="3"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>3</v>
       </c>
@@ -814,8 +850,9 @@
       <c r="C36" s="1">
         <v>8</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D36" s="3"/>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>3</v>
       </c>
@@ -825,8 +862,9 @@
       <c r="C37" s="1">
         <v>8.1999999999999993</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D37" s="3"/>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>3</v>
       </c>
@@ -836,8 +874,9 @@
       <c r="C38" s="1">
         <v>8.4</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D38" s="3"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>3</v>
       </c>
@@ -847,8 +886,9 @@
       <c r="C39" s="1">
         <v>8.6</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D39" s="3"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>3</v>
       </c>
@@ -858,8 +898,9 @@
       <c r="C40" s="1">
         <v>8.8000000000000007</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D40" s="3"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>3</v>
       </c>
@@ -869,8 +910,9 @@
       <c r="C41" s="1">
         <v>9</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D41" s="3"/>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>3</v>
       </c>
@@ -880,8 +922,9 @@
       <c r="C42" s="1">
         <v>9.1999999999999993</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D42" s="3"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>3</v>
       </c>
@@ -891,8 +934,9 @@
       <c r="C43" s="1">
         <v>9.4</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D43" s="3"/>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>3</v>
       </c>
@@ -902,8 +946,9 @@
       <c r="C44" s="1">
         <v>9.6</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D44" s="3"/>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>3</v>
       </c>
@@ -913,8 +958,9 @@
       <c r="C45" s="1">
         <v>9.8000000000000007</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D45" s="3"/>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>3</v>
       </c>
@@ -924,8 +970,9 @@
       <c r="C46" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D46" s="3"/>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>3</v>
       </c>
@@ -935,8 +982,9 @@
       <c r="C47" s="1">
         <v>10.199999999999999</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D47" s="3"/>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>3</v>
       </c>
@@ -946,6 +994,7 @@
       <c r="C48" s="1">
         <v>10.4</v>
       </c>
+      <c r="D48" s="3"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
@@ -957,6 +1006,7 @@
       <c r="C49" s="1">
         <v>10.6</v>
       </c>
+      <c r="D49" s="3"/>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
@@ -968,6 +1018,7 @@
       <c r="C50" s="1">
         <v>10.8</v>
       </c>
+      <c r="D50" s="3"/>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
@@ -979,6 +1030,7 @@
       <c r="C51" s="1">
         <v>11</v>
       </c>
+      <c r="D51" s="3"/>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
@@ -990,6 +1042,7 @@
       <c r="C52" s="1">
         <v>11.2</v>
       </c>
+      <c r="D52" s="3"/>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
@@ -1001,6 +1054,7 @@
       <c r="C53" s="1">
         <v>11.4</v>
       </c>
+      <c r="D53" s="3"/>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
@@ -1012,6 +1066,7 @@
       <c r="C54" s="1">
         <v>11.6</v>
       </c>
+      <c r="D54" s="3"/>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
@@ -1023,6 +1078,7 @@
       <c r="C55" s="1">
         <v>11.8</v>
       </c>
+      <c r="D55" s="3"/>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
@@ -1034,6 +1090,7 @@
       <c r="C56" s="1">
         <v>12</v>
       </c>
+      <c r="D56" s="3"/>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
@@ -1045,6 +1102,7 @@
       <c r="C57" s="1">
         <v>12.2</v>
       </c>
+      <c r="D57" s="3"/>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
@@ -1056,6 +1114,7 @@
       <c r="C58" s="1">
         <v>12.4</v>
       </c>
+      <c r="D58" s="3"/>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
@@ -1067,6 +1126,7 @@
       <c r="C59" s="1">
         <v>12.6</v>
       </c>
+      <c r="D59" s="3"/>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
@@ -1078,6 +1138,7 @@
       <c r="C60" s="1">
         <v>12.8</v>
       </c>
+      <c r="D60" s="3"/>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
@@ -1089,7 +1150,7 @@
       <c r="C61" s="1">
         <v>13</v>
       </c>
-      <c r="D61">
+      <c r="D61" s="3">
         <v>1121894592</v>
       </c>
     </row>
@@ -1103,6 +1164,7 @@
       <c r="C62" s="1">
         <v>13.2</v>
       </c>
+      <c r="D62" s="3"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
@@ -1114,6 +1176,7 @@
       <c r="C63" s="1">
         <v>13.4</v>
       </c>
+      <c r="D63" s="3"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
@@ -1125,8 +1188,9 @@
       <c r="C64" s="1">
         <v>13.6</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D64" s="3"/>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>2</v>
       </c>
@@ -1136,8 +1200,9 @@
       <c r="C65" s="1">
         <v>13.8</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D65" s="3"/>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>2</v>
       </c>
@@ -1147,8 +1212,9 @@
       <c r="C66" s="1">
         <v>14</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D66" s="3"/>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>2</v>
       </c>
@@ -1158,8 +1224,9 @@
       <c r="C67" s="1">
         <v>14.2</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D67" s="3"/>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>2</v>
       </c>
@@ -1169,8 +1236,9 @@
       <c r="C68" s="1">
         <v>14.4</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D68" s="3"/>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>2</v>
       </c>
@@ -1180,8 +1248,9 @@
       <c r="C69" s="1">
         <v>14.6</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D69" s="3"/>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>2</v>
       </c>
@@ -1191,8 +1260,9 @@
       <c r="C70" s="1">
         <v>14.8</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D70" s="3"/>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>2</v>
       </c>
@@ -1202,8 +1272,9 @@
       <c r="C71" s="1">
         <v>15</v>
       </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D71" s="3"/>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>2</v>
       </c>
@@ -1213,8 +1284,9 @@
       <c r="C72" s="1">
         <v>15.2</v>
       </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D72" s="3"/>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>2</v>
       </c>
@@ -1224,8 +1296,9 @@
       <c r="C73" s="1">
         <v>15.4</v>
       </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D73" s="3"/>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>2</v>
       </c>
@@ -1235,8 +1308,9 @@
       <c r="C74" s="1">
         <v>15.6</v>
       </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D74" s="3"/>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>2</v>
       </c>
@@ -1246,8 +1320,9 @@
       <c r="C75" s="1">
         <v>15.8</v>
       </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D75" s="3"/>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>2</v>
       </c>
@@ -1257,8 +1332,9 @@
       <c r="C76" s="1">
         <v>16</v>
       </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D76" s="3"/>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>2</v>
       </c>
@@ -1268,8 +1344,9 @@
       <c r="C77" s="1">
         <v>16.2</v>
       </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D77" s="3"/>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>2</v>
       </c>
@@ -1279,8 +1356,9 @@
       <c r="C78" s="1">
         <v>16.399999999999999</v>
       </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D78" s="3"/>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>2</v>
       </c>
@@ -1290,8 +1368,9 @@
       <c r="C79" s="1">
         <v>16.600000000000001</v>
       </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D79" s="3"/>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>2</v>
       </c>
@@ -1301,8 +1380,9 @@
       <c r="C80" s="1">
         <v>16.8</v>
       </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D80" s="3"/>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>2</v>
       </c>
@@ -1312,8 +1392,9 @@
       <c r="C81" s="1">
         <v>17</v>
       </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D81" s="3"/>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>2</v>
       </c>
@@ -1323,8 +1404,9 @@
       <c r="C82" s="1">
         <v>17.2</v>
       </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D82" s="3"/>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>2</v>
       </c>
@@ -1334,8 +1416,9 @@
       <c r="C83" s="1">
         <v>17.399999999999999</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D83" s="3"/>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>2</v>
       </c>
@@ -1345,8 +1428,9 @@
       <c r="C84" s="1">
         <v>17.600000000000001</v>
       </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D84" s="3"/>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>2</v>
       </c>
@@ -1356,8 +1440,9 @@
       <c r="C85" s="1">
         <v>17.8</v>
       </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D85" s="3"/>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>2</v>
       </c>
@@ -1367,8 +1452,9 @@
       <c r="C86" s="1">
         <v>18</v>
       </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D86" s="3"/>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>2</v>
       </c>
@@ -1378,8 +1464,9 @@
       <c r="C87" s="1">
         <v>18.2</v>
       </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D87" s="3"/>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>2</v>
       </c>
@@ -1389,8 +1476,9 @@
       <c r="C88" s="1">
         <v>18.399999999999999</v>
       </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D88" s="3"/>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>2</v>
       </c>
@@ -1400,8 +1488,9 @@
       <c r="C89" s="1">
         <v>18.600000000000001</v>
       </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D89" s="3"/>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>2</v>
       </c>
@@ -1411,8 +1500,9 @@
       <c r="C90" s="1">
         <v>18.8</v>
       </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D90" s="3"/>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>2</v>
       </c>
@@ -1422,8 +1512,9 @@
       <c r="C91" s="1">
         <v>19</v>
       </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D91" s="3"/>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>2</v>
       </c>
@@ -1433,8 +1524,9 @@
       <c r="C92" s="1">
         <v>19.2</v>
       </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D92" s="3"/>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>2</v>
       </c>
@@ -1444,8 +1536,9 @@
       <c r="C93" s="1">
         <v>19.399999999999999</v>
       </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D93" s="3"/>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>2</v>
       </c>
@@ -1455,8 +1548,9 @@
       <c r="C94" s="1">
         <v>19.600000000000001</v>
       </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D94" s="3"/>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>2</v>
       </c>
@@ -1466,8 +1560,9 @@
       <c r="C95" s="1">
         <v>19.8</v>
       </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D95" s="3"/>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>2</v>
       </c>
@@ -1477,8 +1572,9 @@
       <c r="C96" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D96" s="3"/>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>2</v>
       </c>
@@ -1488,8 +1584,9 @@
       <c r="C97" s="1">
         <v>20.2</v>
       </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D97" s="3"/>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>2</v>
       </c>
@@ -1499,8 +1596,9 @@
       <c r="C98" s="1">
         <v>20.399999999999999</v>
       </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D98" s="3"/>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>2</v>
       </c>
@@ -1510,8 +1608,9 @@
       <c r="C99" s="1">
         <v>20.6</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D99" s="3"/>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>2</v>
       </c>
@@ -1521,8 +1620,9 @@
       <c r="C100" s="1">
         <v>20.8</v>
       </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D100" s="3"/>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>2</v>
       </c>
@@ -1532,8 +1632,9 @@
       <c r="C101" s="1">
         <v>21</v>
       </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D101" s="3"/>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>2</v>
       </c>
@@ -1543,8 +1644,9 @@
       <c r="C102" s="1">
         <v>21.2</v>
       </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D102" s="3"/>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>2</v>
       </c>
@@ -1554,8 +1656,9 @@
       <c r="C103" s="1">
         <v>21.4</v>
       </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D103" s="3"/>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>2</v>
       </c>
@@ -1565,8 +1668,9 @@
       <c r="C104" s="1">
         <v>21.6</v>
       </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D104" s="3"/>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>2</v>
       </c>
@@ -1576,8 +1680,9 @@
       <c r="C105" s="1">
         <v>21.8</v>
       </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D105" s="3"/>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>2</v>
       </c>
@@ -1587,8 +1692,9 @@
       <c r="C106" s="1">
         <v>22</v>
       </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D106" s="3"/>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>2</v>
       </c>
@@ -1598,8 +1704,9 @@
       <c r="C107" s="1">
         <v>22.2</v>
       </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D107" s="3"/>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>2</v>
       </c>
@@ -1609,8 +1716,9 @@
       <c r="C108" s="1">
         <v>22.4</v>
       </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D108" s="3"/>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>2</v>
       </c>
@@ -1620,8 +1728,9 @@
       <c r="C109" s="1">
         <v>22.6</v>
       </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D109" s="3"/>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>2</v>
       </c>
@@ -1631,8 +1740,9 @@
       <c r="C110" s="1">
         <v>22.8</v>
       </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D110" s="3"/>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>2</v>
       </c>
@@ -1642,8 +1752,9 @@
       <c r="C111" s="1">
         <v>23</v>
       </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D111" s="3"/>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>2</v>
       </c>
@@ -1653,8 +1764,9 @@
       <c r="C112" s="1">
         <v>23.2</v>
       </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D112" s="3"/>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>2</v>
       </c>
@@ -1664,8 +1776,9 @@
       <c r="C113" s="1">
         <v>23.4</v>
       </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D113" s="3"/>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>1</v>
       </c>
@@ -1675,8 +1788,9 @@
       <c r="C114" s="1">
         <v>23.6</v>
       </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D114" s="3"/>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>1</v>
       </c>
@@ -1686,8 +1800,9 @@
       <c r="C115" s="1">
         <v>23.8</v>
       </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D115" s="3"/>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>1</v>
       </c>
@@ -1697,8 +1812,9 @@
       <c r="C116" s="1">
         <v>24</v>
       </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D116" s="3"/>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>1</v>
       </c>
@@ -1708,8 +1824,9 @@
       <c r="C117" s="1">
         <v>24.2</v>
       </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D117" s="3"/>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>1</v>
       </c>
@@ -1719,8 +1836,9 @@
       <c r="C118" s="1">
         <v>24.4</v>
       </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D118" s="3"/>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>1</v>
       </c>
@@ -1730,8 +1848,9 @@
       <c r="C119" s="1">
         <v>24.6</v>
       </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D119" s="3"/>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>1</v>
       </c>
@@ -1741,8 +1860,9 @@
       <c r="C120" s="1">
         <v>24.8</v>
       </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D120" s="3"/>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>1</v>
       </c>
@@ -1752,8 +1872,9 @@
       <c r="C121" s="1">
         <v>25</v>
       </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D121" s="3"/>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>1</v>
       </c>
@@ -1763,8 +1884,9 @@
       <c r="C122" s="1">
         <v>25.2</v>
       </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D122" s="3"/>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>1</v>
       </c>
@@ -1774,8 +1896,9 @@
       <c r="C123" s="1">
         <v>25.4</v>
       </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D123" s="3"/>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>1</v>
       </c>
@@ -1785,8 +1908,9 @@
       <c r="C124" s="1">
         <v>25.6</v>
       </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D124" s="3"/>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>1</v>
       </c>
@@ -1796,8 +1920,9 @@
       <c r="C125" s="1">
         <v>25.8</v>
       </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D125" s="3"/>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>1</v>
       </c>
@@ -1807,8 +1932,9 @@
       <c r="C126" s="1">
         <v>26</v>
       </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D126" s="3"/>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>1</v>
       </c>
@@ -1818,8 +1944,9 @@
       <c r="C127" s="1">
         <v>26.2</v>
       </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D127" s="3"/>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>1</v>
       </c>
@@ -1829,8 +1956,9 @@
       <c r="C128" s="1">
         <v>26.4</v>
       </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D128" s="3"/>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>1</v>
       </c>
@@ -1840,8 +1968,9 @@
       <c r="C129" s="1">
         <v>26.6</v>
       </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D129" s="3"/>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>1</v>
       </c>
@@ -1851,8 +1980,9 @@
       <c r="C130" s="1">
         <v>26.8</v>
       </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D130" s="3"/>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>1</v>
       </c>
@@ -1862,8 +1992,9 @@
       <c r="C131" s="1">
         <v>27</v>
       </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D131" s="3"/>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>1</v>
       </c>
@@ -1873,8 +2004,9 @@
       <c r="C132" s="1">
         <v>27.2</v>
       </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D132" s="3"/>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>1</v>
       </c>
@@ -1884,8 +2016,9 @@
       <c r="C133" s="1">
         <v>27.4</v>
       </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D133" s="3"/>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>1</v>
       </c>
@@ -1895,8 +2028,9 @@
       <c r="C134" s="1">
         <v>27.6</v>
       </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D134" s="3"/>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>1</v>
       </c>
@@ -1906,8 +2040,9 @@
       <c r="C135" s="1">
         <v>27.8</v>
       </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D135" s="3"/>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>1</v>
       </c>
@@ -1917,8 +2052,9 @@
       <c r="C136" s="1">
         <v>28</v>
       </c>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D136" s="3"/>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>1</v>
       </c>
@@ -1928,8 +2064,9 @@
       <c r="C137" s="1">
         <v>28.2</v>
       </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D137" s="3"/>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>1</v>
       </c>
@@ -1939,8 +2076,9 @@
       <c r="C138" s="1">
         <v>28.4</v>
       </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D138" s="3"/>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>1</v>
       </c>
@@ -1950,8 +2088,9 @@
       <c r="C139" s="1">
         <v>28.6</v>
       </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D139" s="3"/>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>1</v>
       </c>
@@ -1961,8 +2100,9 @@
       <c r="C140" s="1">
         <v>28.8</v>
       </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D140" s="3"/>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>1</v>
       </c>
@@ -1972,8 +2112,9 @@
       <c r="C141" s="1">
         <v>29</v>
       </c>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D141" s="3"/>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>1</v>
       </c>
@@ -1983,8 +2124,9 @@
       <c r="C142" s="1">
         <v>29.2</v>
       </c>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D142" s="3"/>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>1</v>
       </c>
@@ -1994,8 +2136,9 @@
       <c r="C143" s="1">
         <v>29.4</v>
       </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D143" s="3"/>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>1</v>
       </c>
@@ -2005,8 +2148,9 @@
       <c r="C144" s="1">
         <v>29.6</v>
       </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D144" s="3"/>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>1</v>
       </c>
@@ -2016,8 +2160,9 @@
       <c r="C145" s="1">
         <v>29.8</v>
       </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D145" s="3"/>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>1</v>
       </c>
@@ -2027,8 +2172,9 @@
       <c r="C146" s="1">
         <v>30</v>
       </c>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D146" s="3"/>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>1</v>
       </c>
@@ -2038,8 +2184,9 @@
       <c r="C147" s="1">
         <v>30.2</v>
       </c>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D147" s="3"/>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>1</v>
       </c>
@@ -2049,8 +2196,9 @@
       <c r="C148" s="1">
         <v>30.4</v>
       </c>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D148" s="3"/>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>1</v>
       </c>
@@ -2060,8 +2208,9 @@
       <c r="C149" s="1">
         <v>30.6</v>
       </c>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D149" s="3"/>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>1</v>
       </c>
@@ -2071,8 +2220,9 @@
       <c r="C150" s="1">
         <v>30.8</v>
       </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D150" s="3"/>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>1</v>
       </c>
@@ -2082,8 +2232,9 @@
       <c r="C151" s="1">
         <v>31</v>
       </c>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D151" s="3"/>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>1</v>
       </c>
@@ -2093,8 +2244,9 @@
       <c r="C152" s="1">
         <v>31.2</v>
       </c>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D152" s="3"/>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>1</v>
       </c>
@@ -2104,8 +2256,9 @@
       <c r="C153" s="1">
         <v>31.4</v>
       </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D153" s="3"/>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>1</v>
       </c>
@@ -2115,8 +2268,9 @@
       <c r="C154" s="1">
         <v>31.6</v>
       </c>
-    </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D154" s="3"/>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>1</v>
       </c>
@@ -2126,8 +2280,9 @@
       <c r="C155" s="1">
         <v>31.8</v>
       </c>
-    </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D155" s="3"/>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>1</v>
       </c>
@@ -2137,8 +2292,9 @@
       <c r="C156" s="1">
         <v>32</v>
       </c>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D156" s="3"/>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>1</v>
       </c>
@@ -2148,8 +2304,9 @@
       <c r="C157" s="1">
         <v>32.200000000000003</v>
       </c>
-    </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D157" s="3"/>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>1</v>
       </c>
@@ -2159,8 +2316,9 @@
       <c r="C158" s="1">
         <v>32.4</v>
       </c>
-    </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D158" s="3"/>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>1</v>
       </c>
@@ -2170,8 +2328,9 @@
       <c r="C159" s="1">
         <v>32.6</v>
       </c>
-    </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D159" s="3"/>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>1</v>
       </c>
@@ -2181,8 +2340,9 @@
       <c r="C160" s="1">
         <v>32.799999999999997</v>
       </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D160" s="3"/>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>1</v>
       </c>
@@ -2192,8 +2352,9 @@
       <c r="C161" s="1">
         <v>33</v>
       </c>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D161" s="3"/>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>1</v>
       </c>
@@ -2203,8 +2364,9 @@
       <c r="C162" s="1">
         <v>33.200000000000003</v>
       </c>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D162" s="3"/>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>1</v>
       </c>
@@ -2214,8 +2376,9 @@
       <c r="C163" s="1">
         <v>33.4</v>
       </c>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D163" s="3"/>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>1</v>
       </c>
@@ -2225,8 +2388,9 @@
       <c r="C164" s="1">
         <v>33.6</v>
       </c>
-    </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D164" s="3"/>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>1</v>
       </c>
@@ -2236,8 +2400,9 @@
       <c r="C165" s="1">
         <v>33.799999999999997</v>
       </c>
-    </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D165" s="3"/>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>1</v>
       </c>
@@ -2247,8 +2412,9 @@
       <c r="C166" s="1">
         <v>34</v>
       </c>
-    </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D166" s="3"/>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>1</v>
       </c>
@@ -2258,8 +2424,9 @@
       <c r="C167" s="1">
         <v>34.200000000000003</v>
       </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D167" s="3"/>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>1</v>
       </c>
@@ -2269,8 +2436,9 @@
       <c r="C168" s="1">
         <v>34.4</v>
       </c>
-    </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D168" s="3"/>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>1</v>
       </c>
@@ -2280,8 +2448,9 @@
       <c r="C169" s="1">
         <v>34.6</v>
       </c>
-    </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D169" s="3"/>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>0</v>
       </c>
@@ -2291,8 +2460,9 @@
       <c r="C170" s="1">
         <v>34.799999999999997</v>
       </c>
-    </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D170" s="3"/>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>0</v>
       </c>
@@ -2302,8 +2472,9 @@
       <c r="C171" s="1">
         <v>35</v>
       </c>
-    </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D171" s="3"/>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>0</v>
       </c>
@@ -2313,8 +2484,9 @@
       <c r="C172" s="1">
         <v>35.200000000000003</v>
       </c>
-    </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D172" s="3"/>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>0</v>
       </c>
@@ -2324,8 +2496,9 @@
       <c r="C173" s="1">
         <v>35.4</v>
       </c>
-    </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D173" s="3"/>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>0</v>
       </c>
@@ -2335,8 +2508,9 @@
       <c r="C174" s="1">
         <v>35.6</v>
       </c>
-    </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D174" s="3"/>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>0</v>
       </c>
@@ -2346,8 +2520,9 @@
       <c r="C175" s="1">
         <v>35.799999999999997</v>
       </c>
-    </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D175" s="3"/>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>0</v>
       </c>
@@ -2357,8 +2532,9 @@
       <c r="C176" s="1">
         <v>36</v>
       </c>
-    </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D176" s="3"/>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>0</v>
       </c>
@@ -2368,8 +2544,9 @@
       <c r="C177" s="1">
         <v>36.200000000000003</v>
       </c>
-    </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D177" s="3"/>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>0</v>
       </c>
@@ -2379,8 +2556,9 @@
       <c r="C178" s="1">
         <v>36.4</v>
       </c>
-    </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D178" s="3"/>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>0</v>
       </c>
@@ -2390,8 +2568,9 @@
       <c r="C179" s="1">
         <v>36.6</v>
       </c>
-    </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D179" s="3"/>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>0</v>
       </c>
@@ -2401,8 +2580,9 @@
       <c r="C180" s="1">
         <v>36.799999999999997</v>
       </c>
-    </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D180" s="3"/>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>0</v>
       </c>
@@ -2412,8 +2592,9 @@
       <c r="C181" s="1">
         <v>37</v>
       </c>
-    </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D181" s="3"/>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>0</v>
       </c>
@@ -2423,8 +2604,9 @@
       <c r="C182" s="1">
         <v>37.200000000000003</v>
       </c>
-    </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D182" s="3"/>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>0</v>
       </c>
@@ -2434,8 +2616,9 @@
       <c r="C183" s="1">
         <v>37.4</v>
       </c>
-    </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D183" s="3"/>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>0</v>
       </c>
@@ -2445,8 +2628,9 @@
       <c r="C184" s="1">
         <v>37.6</v>
       </c>
-    </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D184" s="3"/>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>0</v>
       </c>
@@ -2456,8 +2640,9 @@
       <c r="C185" s="1">
         <v>37.799999999999997</v>
       </c>
-    </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D185" s="3"/>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>0</v>
       </c>
@@ -2467,8 +2652,9 @@
       <c r="C186" s="1">
         <v>38</v>
       </c>
-    </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D186" s="3"/>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>0</v>
       </c>
@@ -2478,8 +2664,9 @@
       <c r="C187" s="1">
         <v>38.200000000000003</v>
       </c>
-    </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D187" s="3"/>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>0</v>
       </c>
@@ -2489,8 +2676,9 @@
       <c r="C188" s="1">
         <v>38.4</v>
       </c>
-    </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D188" s="3"/>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>0</v>
       </c>
@@ -2500,8 +2688,9 @@
       <c r="C189" s="1">
         <v>38.6</v>
       </c>
-    </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D189" s="3"/>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>0</v>
       </c>
@@ -2511,8 +2700,9 @@
       <c r="C190" s="1">
         <v>38.799999999999997</v>
       </c>
-    </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D190" s="3"/>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>0</v>
       </c>
@@ -2522,8 +2712,9 @@
       <c r="C191" s="1">
         <v>39</v>
       </c>
-    </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D191" s="3"/>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>0</v>
       </c>
@@ -2533,8 +2724,9 @@
       <c r="C192" s="1">
         <v>39.200000000000003</v>
       </c>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D192" s="3"/>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>0</v>
       </c>
@@ -2544,8 +2736,9 @@
       <c r="C193" s="1">
         <v>39.4</v>
       </c>
-    </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D193" s="3"/>
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>0</v>
       </c>
@@ -2555,8 +2748,9 @@
       <c r="C194" s="1">
         <v>39.6</v>
       </c>
-    </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D194" s="3"/>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>0</v>
       </c>
@@ -2566,8 +2760,9 @@
       <c r="C195" s="1">
         <v>39.799999999999997</v>
       </c>
-    </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D195" s="3"/>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>0</v>
       </c>
@@ -2577,8 +2772,9 @@
       <c r="C196" s="1">
         <v>40</v>
       </c>
-    </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D196" s="3"/>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>0</v>
       </c>
@@ -2588,8 +2784,9 @@
       <c r="C197" s="1">
         <v>40.200000000000003</v>
       </c>
-    </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D197" s="3"/>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>0</v>
       </c>
@@ -2599,8 +2796,9 @@
       <c r="C198" s="1">
         <v>40.4</v>
       </c>
-    </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D198" s="3"/>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>0</v>
       </c>
@@ -2610,8 +2808,9 @@
       <c r="C199" s="1">
         <v>40.6</v>
       </c>
-    </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D199" s="3"/>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>0</v>
       </c>
@@ -2621,8 +2820,9 @@
       <c r="C200" s="1">
         <v>40.799999999999997</v>
       </c>
-    </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D200" s="3"/>
+    </row>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>0</v>
       </c>
@@ -2632,8 +2832,9 @@
       <c r="C201" s="1">
         <v>41</v>
       </c>
-    </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D201" s="3"/>
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>0</v>
       </c>
@@ -2643,8 +2844,9 @@
       <c r="C202" s="1">
         <v>41.2</v>
       </c>
-    </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D202" s="3"/>
+    </row>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>0</v>
       </c>
@@ -2654,8 +2856,9 @@
       <c r="C203" s="1">
         <v>41.4</v>
       </c>
-    </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D203" s="3"/>
+    </row>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>0</v>
       </c>
@@ -2665,8 +2868,9 @@
       <c r="C204" s="1">
         <v>41.6</v>
       </c>
-    </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D204" s="3"/>
+    </row>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>0</v>
       </c>
@@ -2676,8 +2880,9 @@
       <c r="C205" s="1">
         <v>41.8</v>
       </c>
-    </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D205" s="3"/>
+    </row>
+    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>0</v>
       </c>
@@ -2687,8 +2892,9 @@
       <c r="C206" s="1">
         <v>42</v>
       </c>
-    </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D206" s="3"/>
+    </row>
+    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>0</v>
       </c>
@@ -2698,8 +2904,9 @@
       <c r="C207" s="1">
         <v>42.2</v>
       </c>
-    </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D207" s="3"/>
+    </row>
+    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>0</v>
       </c>
@@ -2709,8 +2916,9 @@
       <c r="C208" s="1">
         <v>42.4</v>
       </c>
-    </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D208" s="3"/>
+    </row>
+    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>0</v>
       </c>
@@ -2720,8 +2928,9 @@
       <c r="C209" s="1">
         <v>42.6</v>
       </c>
-    </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D209" s="3"/>
+    </row>
+    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>0</v>
       </c>
@@ -2731,8 +2940,9 @@
       <c r="C210" s="1">
         <v>42.8</v>
       </c>
-    </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D210" s="3"/>
+    </row>
+    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>0</v>
       </c>
@@ -2742,8 +2952,9 @@
       <c r="C211" s="1">
         <v>43</v>
       </c>
-    </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D211" s="3"/>
+    </row>
+    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>0</v>
       </c>
@@ -2753,8 +2964,9 @@
       <c r="C212" s="1">
         <v>43.2</v>
       </c>
-    </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D212" s="3"/>
+    </row>
+    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>0</v>
       </c>
@@ -2764,8 +2976,9 @@
       <c r="C213" s="1">
         <v>43.4</v>
       </c>
-    </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D213" s="3"/>
+    </row>
+    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>0</v>
       </c>
@@ -2775,8 +2988,9 @@
       <c r="C214" s="1">
         <v>43.6</v>
       </c>
-    </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D214" s="3"/>
+    </row>
+    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>0</v>
       </c>
@@ -2786,8 +3000,9 @@
       <c r="C215" s="1">
         <v>43.8</v>
       </c>
-    </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D215" s="3"/>
+    </row>
+    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>0</v>
       </c>
@@ -2797,8 +3012,9 @@
       <c r="C216" s="1">
         <v>44</v>
       </c>
-    </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D216" s="3"/>
+    </row>
+    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>0</v>
       </c>
@@ -2808,8 +3024,9 @@
       <c r="C217" s="1">
         <v>44.2</v>
       </c>
-    </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D217" s="3"/>
+    </row>
+    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>0</v>
       </c>
@@ -2819,8 +3036,9 @@
       <c r="C218" s="1">
         <v>44.4</v>
       </c>
-    </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D218" s="3"/>
+    </row>
+    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>0</v>
       </c>
@@ -2830,8 +3048,9 @@
       <c r="C219" s="1">
         <v>44.6</v>
       </c>
-    </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D219" s="3"/>
+    </row>
+    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>0</v>
       </c>
@@ -2841,8 +3060,9 @@
       <c r="C220" s="1">
         <v>44.8</v>
       </c>
-    </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D220" s="3"/>
+    </row>
+    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>0</v>
       </c>
@@ -2852,8 +3072,9 @@
       <c r="C221" s="1">
         <v>45</v>
       </c>
-    </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D221" s="3"/>
+    </row>
+    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>0</v>
       </c>
@@ -2863,8 +3084,9 @@
       <c r="C222" s="1">
         <v>45.2</v>
       </c>
-    </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D222" s="3"/>
+    </row>
+    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>0</v>
       </c>
@@ -2874,8 +3096,9 @@
       <c r="C223" s="1">
         <v>45.4</v>
       </c>
-    </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D223" s="3"/>
+    </row>
+    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>0</v>
       </c>
@@ -2885,8 +3108,9 @@
       <c r="C224" s="1">
         <v>45.6</v>
       </c>
-    </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D224" s="3"/>
+    </row>
+    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>0</v>
       </c>
@@ -2896,6 +3120,7 @@
       <c r="C225" s="1">
         <v>45.8</v>
       </c>
+      <c r="D225" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/censo.xlsx
+++ b/censo.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="12">
   <si>
     <t>T10</t>
   </si>
@@ -48,6 +48,18 @@
   </si>
   <si>
     <t>Apoderado_ID</t>
+  </si>
+  <si>
+    <t>1321312121</t>
+  </si>
+  <si>
+    <t>11111111111</t>
+  </si>
+  <si>
+    <t>111111111</t>
+  </si>
+  <si>
+    <t>22222222</t>
   </si>
 </sst>
 </file>
@@ -83,7 +95,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -92,6 +104,7 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -438,7 +451,9 @@
       <c r="C2" s="1">
         <v>1.2</v>
       </c>
-      <c r="D2" s="3"/>
+      <c r="D2" s="4">
+        <v>1234567890</v>
+      </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -462,7 +477,9 @@
       <c r="C4" s="1">
         <v>1.45</v>
       </c>
-      <c r="D4" s="3"/>
+      <c r="D4" s="4">
+        <v>1013615339</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -1572,7 +1589,9 @@
       <c r="C96" s="1">
         <v>20</v>
       </c>
-      <c r="D96" s="3"/>
+      <c r="D96" s="4">
+        <v>555555555</v>
+      </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
@@ -2064,7 +2083,9 @@
       <c r="C137" s="1">
         <v>28.2</v>
       </c>
-      <c r="D137" s="3"/>
+      <c r="D137" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
@@ -2436,7 +2457,9 @@
       <c r="C168" s="1">
         <v>34.4</v>
       </c>
-      <c r="D168" s="3"/>
+      <c r="D168" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
@@ -2544,7 +2567,9 @@
       <c r="C177" s="1">
         <v>36.200000000000003</v>
       </c>
-      <c r="D177" s="3"/>
+      <c r="D177" s="3" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
@@ -2796,7 +2821,9 @@
       <c r="C198" s="1">
         <v>40.4</v>
       </c>
-      <c r="D198" s="3"/>
+      <c r="D198" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
